--- a/assets/visual-resource/narrator/UCRUWY5mDSRMce7hOeLljDbg/UCRUWY5mDSRMce7hOeLljDbg.xlsx
+++ b/assets/visual-resource/narrator/UCRUWY5mDSRMce7hOeLljDbg/UCRUWY5mDSRMce7hOeLljDbg.xlsx
@@ -7026,7 +7026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1138"/>
+  <dimension ref="A1:C1138"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -7537,12 +7537,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>126</v>
       </c>
       <c r="B64" t="s">
         <v>127</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -8017,12 +8020,15 @@
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>244</v>
       </c>
       <c r="B124" t="s">
         <v>245</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -8145,12 +8151,15 @@
         <v>275</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>276</v>
       </c>
       <c r="B140" t="s">
         <v>277</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -8833,12 +8842,15 @@
         <v>446</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>447</v>
       </c>
       <c r="B226" t="s">
         <v>448</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -9665,12 +9677,15 @@
         <v>652</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>653</v>
       </c>
       <c r="B330" t="s">
         <v>654</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -10481,12 +10496,15 @@
         <v>853</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>854</v>
       </c>
       <c r="B432" t="s">
         <v>855</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -11033,12 +11051,15 @@
         <v>987</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>988</v>
       </c>
       <c r="B501" t="s">
         <v>989</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
@@ -11713,12 +11734,15 @@
         <v>544</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>1150</v>
       </c>
       <c r="B586" t="s">
         <v>1151</v>
+      </c>
+      <c r="C586">
+        <v>1</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
@@ -12505,12 +12529,15 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>1341</v>
       </c>
       <c r="B685" t="s">
         <v>1342</v>
+      </c>
+      <c r="C685">
+        <v>1</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.25">
@@ -12529,12 +12556,15 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>1347</v>
       </c>
       <c r="B688" t="s">
         <v>1348</v>
+      </c>
+      <c r="C688">
+        <v>1</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.25">
@@ -13849,12 +13879,15 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="853" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>1668</v>
       </c>
       <c r="B853" t="s">
         <v>1669</v>
+      </c>
+      <c r="C853">
+        <v>1</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.25">
@@ -14409,12 +14442,15 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="923" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>1804</v>
       </c>
       <c r="B923" t="s">
         <v>1805</v>
+      </c>
+      <c r="C923">
+        <v>1</v>
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.25">
@@ -15369,12 +15405,15 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="1043" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>2034</v>
       </c>
       <c r="B1043" t="s">
         <v>2035</v>
+      </c>
+      <c r="C1043">
+        <v>1</v>
       </c>
     </row>
     <row r="1044" spans="1:2" x14ac:dyDescent="0.25">
@@ -16139,6 +16178,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/assets/visual-resource/narrator/UCRUWY5mDSRMce7hOeLljDbg/UCRUWY5mDSRMce7hOeLljDbg.xlsx
+++ b/assets/visual-resource/narrator/UCRUWY5mDSRMce7hOeLljDbg/UCRUWY5mDSRMce7hOeLljDbg.xlsx
@@ -11438,12 +11438,15 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1079</v>
       </c>
       <c r="B549" t="s">
         <v>1080</v>
+      </c>
+      <c r="C549">
+        <v>1</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
